--- a/inventory/files/2026-W40/STA_US_LEGACY_2026-W40.xlsx
+++ b/inventory/files/2026-W40/STA_US_LEGACY_2026-W40.xlsx
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>316</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10">
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11">
@@ -1712,37 +1712,37 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>118</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>H-146Q</t>
+          <t>C-102TA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>93</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C-102TA</t>
+          <t>C-246TA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C-244TA</t>
+          <t>C-192TA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -1752,113 +1752,113 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>H-148TA</t>
+          <t>C-241T</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H-146TA</t>
+          <t>C-244TA</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SE-145</t>
+          <t>H-146TA</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C-192TA</t>
+          <t>H-148P</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C-246TA</t>
+          <t>H-109TA</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C-228T</t>
+          <t>H-190P</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>H-TOP3KITA</t>
+          <t>C-128T</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C-7600Q</t>
+          <t>H-TOP3KITA</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>H-261T</t>
+          <t>H-148TA</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>H-221T</t>
+          <t>H-189T</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>H-306T</t>
+          <t>H-166T</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1868,7 +1868,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>H-166T</t>
+          <t>C-7900P</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1878,17 +1878,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>H-363T</t>
+          <t>H-226T</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>H-190Q</t>
+          <t>SE-220</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1898,7 +1898,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>C-112T</t>
+          <t>C-242T</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1908,27 +1908,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>C-140TA</t>
+          <t>H-337T</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>C-112P</t>
+          <t>C-111P</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>H-329T</t>
+          <t>H-144P</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1938,7 +1938,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>H-294P</t>
+          <t>H-316T</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1948,7 +1948,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>H-140T</t>
+          <t>H-144T</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1958,7 +1958,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>H-326T</t>
+          <t>C-112T</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1968,17 +1968,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>H-109TA</t>
+          <t>H-175T</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>H-265P</t>
+          <t>SE-512</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1988,7 +1988,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C-190P</t>
+          <t>H-112T</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1998,7 +1998,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>H-199T</t>
+          <t>H-216P</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -2008,7 +2008,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>H-112T</t>
+          <t>SE-261</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2018,7 +2018,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SE-147B</t>
+          <t>H-212T</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -2028,7 +2028,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>C-8200P</t>
+          <t>SE-147B</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2038,7 +2038,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FX-112A</t>
+          <t>1H-KIT370C241</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -2048,7 +2048,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>H-229T</t>
+          <t>V-171T</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2058,7 +2058,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>C-246P</t>
+          <t>H-151T</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -2068,7 +2068,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>F-102T</t>
+          <t>H-294P</t>
         </is>
       </c>
       <c r="B47" t="n">

--- a/inventory/files/2026-W40/STA_US_LEGACY_2026-W40.xlsx
+++ b/inventory/files/2026-W40/STA_US_LEGACY_2026-W40.xlsx
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10">
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11">
